--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 09:48:59</t>
+          <t>2026-08-25 10:24:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:00</t>
+          <t>2026-08-25 10:24:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:02</t>
+          <t>2026-08-25 10:24:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 09:49:03</t>
+          <t>2026-08-25 10:24:48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2375</t>
+          <t>+1.05%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.74%1,794,000</t>
+          <t>8.67%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.74%</t>
+          <t>8.67%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>+2.22%6440</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3765</v>
+        <v>6440</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.73%872,000</t>
+          <t>6.62%510,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.73%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>872000</v>
+        <v>510000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>-0.8%3735</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6300</v>
+        <v>3735</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.59%510,000</t>
+          <t>6.56%872,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.59%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>510000</v>
+        <v>872000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.52%758</t>
+          <t>+1.32%768</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.95%3,828,000</t>
+          <t>5.96%3,850,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3828000</v>
+        <v>3850000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>-0.87%14285</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14410</v>
+        <v>14285</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.47%185,000</t>
+          <t>5.35%186,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>185000</v>
+        <v>186000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>+6.76%379</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+6.76%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2070</v>
+        <v>379</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.58%844,000</t>
+          <t>3.67%4,809,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>844000</v>
+        <v>4809000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,33 +875,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>+3.04%5595</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+3.04%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5430</v>
+        <v>5595</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.56%320,000</t>
+          <t>3.63%322,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>320000</v>
+        <v>322000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>+0.63%5600</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5565</v>
+        <v>5600</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.50%307,000</t>
+          <t>3.46%307,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,34 +992,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.83%355</t>
+          <t>-5.07%1965</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>355</v>
+        <v>1965</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.50%4,809,000</t>
+          <t>3.36%849,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4809000</v>
+        <v>849000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.72%2070</t>
+          <t>-1.93%2030</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2070</v>
+        <v>2030</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.09%727,000</t>
+          <t>2.97%727,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.3%845</t>
+          <t>+6.22%5720</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>845</v>
+        <v>5720</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.86%1,650,000</t>
+          <t>2.97%258,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1650000</v>
+        <v>258000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>+3.67%876</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>435.5</v>
+        <v>876</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.84%3,178,000</t>
+          <t>2.91%1,650,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.91%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3178000</v>
+        <v>1650000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+1.95%444</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5385</v>
+        <v>444</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.84%257,000</t>
+          <t>2.84%3,178,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>257000</v>
+        <v>3178000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.78%1290</t>
+          <t>-1.55%1270</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1290</v>
+        <v>1270</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.65%1,000,000</t>
+          <t>2.56%1,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:44</t>
+          <t>2026-08-25 17:37:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>+3.33%2950</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1010</v>
+        <v>2950</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.31%1,117,000</t>
+          <t>2.26%381,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1117000</v>
+        <v>381000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,25 +1419,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>-2.97%980</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2855</v>
+        <v>980</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.22%379,000</t>
+          <t>2.22%1,123,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1446,11 +1446,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>379000</v>
+        <v>1123000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.27%688</t>
+          <t>+1.82%670</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.63%1,158,000</t>
+          <t>2.01%1,486,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1158000</v>
+        <v>1486000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.23%205.5</t>
+          <t>+3.14%296</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>205.5</v>
+        <v>296</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.37%3,242,000</t>
+          <t>1.97%3,302,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3242000</v>
+        <v>3302000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.96%287</t>
+          <t>+0.73%693</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>287</v>
+        <v>693</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.35%2,289,000</t>
+          <t>1.62%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2289000</v>
+        <v>1158000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,20 +1668,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>+1.21%125</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>123.5</v>
+        <v>125</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.34%5,285,000</t>
+          <t>1.34%5,315,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5285000</v>
+        <v>5315000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.13%181.5</t>
+          <t>+9.96%419.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>181.5</v>
+        <v>419.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.32%3,533,000</t>
+          <t>1.34%1,581,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3533000</v>
+        <v>1581000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.77%144</t>
+          <t>+0.83%183</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.30%4,386,000</t>
+          <t>1.31%3,552,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4386000</v>
+        <v>3552000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,33 +1851,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+2.06%1485</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1455</v>
+        <v>1485</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.30%434,000</t>
+          <t>1.31%437,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>434000</v>
+        <v>437000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,20 +1912,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%179.5</t>
+          <t>+1.11%181.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%3,504,000</t>
+          <t>1.29%3,524,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3504000</v>
+        <v>3524000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.44%341</t>
+          <t>0%144</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>341</v>
+        <v>144</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.26%1,800,000</t>
+          <t>1.28%4,412,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1800000</v>
+        <v>4412000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%175.5</t>
+          <t>+1.91%347.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>175.5</v>
+        <v>347.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.24%3,432,000</t>
+          <t>1.27%1,811,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3432000</v>
+        <v>1811000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.03%381.5</t>
+          <t>+1.71%178.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>381.5</v>
+        <v>178.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23%1,572,000</t>
+          <t>1.24%3,453,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1572000</v>
+        <v>3453000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.39%658</t>
+          <t>-0.4%249.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>658</v>
+        <v>249.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.22%901,000</t>
+          <t>1.19%2,371,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>901000</v>
+        <v>2371000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.18%250.5</t>
+          <t>+1.2%168</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>250.5</v>
+        <v>168</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.21%2,356,000</t>
+          <t>1.18%3,494,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2356000</v>
+        <v>3494000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:46</t>
+          <t>2026-08-25 17:37:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.9%166</t>
+          <t>-0.17%591</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>166</v>
+        <v>591</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.18%3,472,000</t>
+          <t>1.15%965,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3472000</v>
+        <v>965000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.85%592</t>
+          <t>+1.84%166</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>592</v>
+        <v>166</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.16%959,000</t>
+          <t>1.14%3,416,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>959000</v>
+        <v>3416000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.21%163</t>
+          <t>+1.89%15400</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>163</v>
+        <v>15400</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.14%3,396,000</t>
+          <t>1.11%35,900</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3396000</v>
+        <v>35900</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>0%120.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15115</v>
+        <v>120.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.11%35,900</t>
+          <t>1.09%4,511,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>35900</v>
+        <v>4511000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.43%120.5</t>
+          <t>+0.38%535</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>120.5</v>
+        <v>535</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.11%4,484,000</t>
+          <t>1.08%1,000,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4484000</v>
+        <v>1000000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.82%533</t>
+          <t>+1.48%273.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.82%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>533</v>
+        <v>273.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.09%1,000,000</t>
+          <t>1.05%1,910,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000000</v>
+        <v>1910000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.75%269.5</t>
+          <t>+3.75%470</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>269.5</v>
+        <v>470</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.06%1,910,000</t>
+          <t>0.98%1,032,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1910000</v>
+        <v>1032000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+6.11%1215</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+6.11%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1145</v>
+        <v>1215</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.90%382,000</t>
+          <t>0.94%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.27%860</t>
+          <t>+3.65%213</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>860</v>
+        <v>213</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.81%459,000</t>
+          <t>0.88%2,042,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>459000</v>
+        <v>2042000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.44%453</t>
+          <t>+3.61%258</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>453</v>
+        <v>258</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.72%774,000</t>
+          <t>0.84%1,607,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>774000</v>
+        <v>1607000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.26%249</t>
+          <t>-0.81%853</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>249</v>
+        <v>853</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.49%950,000</t>
+          <t>0.79%459,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>950000</v>
+        <v>459000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.09%2200</t>
+          <t>-0.23%2195</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.42%93,000</t>
+          <t>0.41%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.77%257.5</t>
+          <t>+9.84%530</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>257.5</v>
+        <v>530</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.32%603,000</t>
+          <t>0.34%322,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>603000</v>
+        <v>322000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-5.95%482.5</t>
+          <t>+4.33%120.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>+4.33%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>482.5</v>
+        <v>120.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%321,000</t>
+          <t>0.32%1,311,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>321000</v>
+        <v>1311000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.51%493</t>
+          <t>-3.88%247.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>493</v>
+        <v>247.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.31%310,000</t>
+          <t>0.31%612,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>310000</v>
+        <v>612000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:47</t>
+          <t>2026-08-25 17:37:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.86%115.5</t>
+          <t>-3.25%477</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>115.5</v>
+        <v>477</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%1,303,000</t>
+          <t>0.30%312,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1303000</v>
+        <v>312000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,33 +3254,33 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.18%259</t>
+          <t>+4.44%270.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.18%</t>
+          <t>+4.44%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>259</v>
+        <v>270.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.29%546,000</t>
+          <t>0.30%549,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>546000</v>
+        <v>549000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,20 +3315,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.41%49</t>
+          <t>+0.61%49.3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.29%2,871,000</t>
+          <t>0.29%2,897,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2871000</v>
+        <v>2897000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.5%62.4</t>
+          <t>0%62.4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,33 +3437,33 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.38%86.1</t>
+          <t>+2.09%87.9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>86.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.27%1,544,000</t>
+          <t>0.28%1,563,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1544000</v>
+        <v>1563000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+5.36%1475</t>
+          <t>+1.02%1490</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+5.36%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1475</v>
+        <v>1490</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.63%47.2</t>
+          <t>+1.8%48.05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47.2</v>
+        <v>48.05</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-4.2%5365</t>
+          <t>+3.82%5570</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.82%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5365</v>
+        <v>5570</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.2%1160</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1135</v>
+        <v>1160</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-2.75%177</t>
+          <t>-0.56%176</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-1.52%712</t>
+          <t>+0.7%717</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-4.36%417</t>
+          <t>+2.88%429</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>+2.88%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+2.33%92.1</t>
+          <t>-0.76%91.4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+2.33%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>92.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3986,16 +3986,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-0.21%46.85</t>
+          <t>+0.32%47</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>46.85</v>
+        <v>47</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 10:24:48</t>
+          <t>2026-08-25 17:37:23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4047,16 +4047,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-1.49%132</t>
+          <t>+7.2%141.5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>132</v>
+        <v>141.5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:19</t>
+          <t>2026-08-25 19:51:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:21</t>
+          <t>2026-08-25 19:51:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:22</t>
+          <t>2026-08-25 19:51:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 17:37:23</t>
+          <t>2026-08-25 19:51:23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:19</t>
+          <t>2026-08-25 21:09:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:20</t>
+          <t>2026-08-25 21:09:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:22</t>
+          <t>2026-08-25 21:09:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 19:51:23</t>
+          <t>2026-08-25 21:09:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:41</t>
+          <t>2026-08-25 21:28:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:43</t>
+          <t>2026-08-25 21:28:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:44</t>
+          <t>2026-08-25 21:28:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:09:45</t>
+          <t>2026-08-25 21:28:19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:15</t>
+          <t>2026-08-25 21:31:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:16</t>
+          <t>2026-08-25 21:31:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:18</t>
+          <t>2026-08-25 21:31:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:28:19</t>
+          <t>2026-08-25 21:31:41</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-25_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:37</t>
+          <t>2026-08-25 22:04:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:39</t>
+          <t>2026-08-25 22:04:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:40</t>
+          <t>2026-08-25 22:04:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-25 21:31:41</t>
+          <t>2026-08-25 22:04:25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
